--- a/fix-mapping-entete-duplicate-targets/ig/FRPatientLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRPatientLMCDAFHIR.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:43:57+00:00</t>
+    <t>2026-09-02T12:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
   <si>
     <t xml:space="preserve">Ce ConceptMap présente deux groupes de mapping :
  - Mapping 1 : entre le modèle métier \"FRLMPatient\" et l'élément CDA \"recordTarget\"
- - Mapping 2 : entre le modèle métier \"FRLMPatient\" et le profil FHIR \"FrPatientDocument\" </t>
+ - Mapping 2 : entre le modèle métier \"FRLMPatient\" et le profil FHIR \"FRPatientINSDocument\" </t>
   </si>
   <si>
     <t>Purpose</t>
@@ -159,6 +159,9 @@
     <t>FRLMPatient.name</t>
   </si>
   <si>
+    <t>FRLMHumanName</t>
+  </si>
+  <si>
     <t>Patient.name</t>
   </si>
   <si>
@@ -244,6 +247,9 @@
   </si>
   <si>
     <t>Patient</t>
+  </si>
+  <si>
+    <t>FRPatientINSDocument</t>
   </si>
   <si>
     <t>Patient.identifier</t>
@@ -727,168 +733,170 @@
       <c r="A3" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" t="s" s="2">
+        <v>46</v>
+      </c>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E15" s="2"/>
     </row>
@@ -921,7 +929,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -938,40 +946,40 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -1013,7 +1021,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -1028,9 +1036,11 @@
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>76</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -1041,7 +1051,7 @@
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E4" s="2"/>
     </row>
@@ -1054,7 +1064,7 @@
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -1067,7 +1077,7 @@
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -1075,12 +1085,14 @@
       <c r="A7" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>46</v>
+      </c>
       <c r="C7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -1088,142 +1100,144 @@
       <c r="A8" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" t="s" s="2">
+        <v>46</v>
+      </c>
       <c r="C8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E18" s="2"/>
     </row>

--- a/fix-mapping-entete-duplicate-targets/ig/FRPatientLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRPatientLMCDAFHIR.xlsx
@@ -12,12 +12,13 @@
     <sheet name="Mapping Table 2" r:id="rId6" sheetId="4"/>
     <sheet name="Mapping Table 3" r:id="rId7" sheetId="5"/>
     <sheet name="Mapping Table 4" r:id="rId8" sheetId="6"/>
+    <sheet name="Mapping Table 5" r:id="rId9" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T12:54:48+00:00</t>
+    <t>2026-09-02T15:48:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -165,6 +166,27 @@
     <t>Patient.name</t>
   </si>
   <si>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHumanName|0.1.0</t>
+  </si>
+  <si>
+    <t>FRLMHumanName.use</t>
+  </si>
+  <si>
+    <t>Patient.name.use</t>
+  </si>
+  <si>
+    <t>FRLMHumanName.family</t>
+  </si>
+  <si>
+    <t>Patient.name.item.family</t>
+  </si>
+  <si>
+    <t>FRLMHumanName.given</t>
+  </si>
+  <si>
+    <t>Patient.name.item.given</t>
+  </si>
+  <si>
     <t>FRLMPatient.administrativeGender</t>
   </si>
   <si>
@@ -220,27 +242,6 @@
   </si>
   <si>
     <t>FRLMPatient.contact.organization</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHumanName|0.1.0</t>
-  </si>
-  <si>
-    <t>FRLMHumanName.use</t>
-  </si>
-  <si>
-    <t>Patient.name.use</t>
-  </si>
-  <si>
-    <t>FRLMHumanName.family</t>
-  </si>
-  <si>
-    <t>Patient.name.item.family</t>
-  </si>
-  <si>
-    <t>FRLMHumanName.given</t>
-  </si>
-  <si>
-    <t>Patient.name.item.given</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-ins-document|0.1.0</t>
@@ -692,7 +693,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -743,162 +744,6 @@
         <v>47</v>
       </c>
       <c r="E3" s="2"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="D15" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="E15" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -929,7 +774,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -946,40 +791,40 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -990,6 +835,206 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
@@ -1113,7 +1158,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
@@ -1126,7 +1171,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
@@ -1139,7 +1184,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
@@ -1152,7 +1197,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
@@ -1165,7 +1210,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
@@ -1178,7 +1223,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
@@ -1191,7 +1236,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
@@ -1204,7 +1249,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -1217,7 +1262,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -1230,7 +1275,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">

--- a/fix-mapping-entete-duplicate-targets/ig/FRPatientLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRPatientLMCDAFHIR.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:48:56+00:00</t>
+    <t>2026-09-03T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-mapping-entete-duplicate-targets/ig/FRPatientLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRPatientLMCDAFHIR.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:02:14+00:00</t>
+    <t>2026-09-03T10:35:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-mapping-entete-duplicate-targets/ig/FRPatientLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRPatientLMCDAFHIR.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:35:28+00:00</t>
+    <t>2026-09-04T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
